--- a/clean/chemistry/chem_water_analysis_2025.xlsx
+++ b/clean/chemistry/chem_water_analysis_2025.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'data'!$A$1:$BF$358</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'data'!$A$1:$BH$358</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF358"/>
+  <dimension ref="A1:BH358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -502,6 +502,8 @@
     <col width="27" customWidth="1" min="56" max="56"/>
     <col width="15" customWidth="1" min="57" max="57"/>
     <col width="48" customWidth="1" min="58" max="58"/>
+    <col width="29" customWidth="1" min="59" max="59"/>
+    <col width="17" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -795,6 +797,16 @@
           <t>sample_name_group</t>
         </is>
       </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>sector_flag</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -971,6 +983,11 @@
           <t>مياة حنفية للغسيل</t>
         </is>
       </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1147,6 +1164,11 @@
           <t>مياة غسيل حنفية</t>
         </is>
       </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1323,6 +1345,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1499,6 +1526,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1675,6 +1707,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1851,6 +1888,11 @@
           <t>مياة حنفية للطبخ</t>
         </is>
       </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2027,6 +2069,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2213,6 +2260,11 @@
           <t>مياة حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2399,6 +2451,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2585,6 +2642,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2771,6 +2833,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2957,6 +3024,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3143,6 +3215,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3329,6 +3406,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3515,6 +3597,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3701,6 +3788,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3887,6 +3979,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4068,6 +4165,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4249,6 +4351,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4435,6 +4542,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4621,6 +4733,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4807,6 +4924,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4993,6 +5115,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5179,6 +5306,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5360,6 +5492,11 @@
           <t>مياه معاباة للعجانة</t>
         </is>
       </c>
+      <c r="BG26" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5541,6 +5678,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG27" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5719,6 +5861,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG28" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5900,6 +6047,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG29" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6081,6 +6233,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG30" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6272,6 +6429,11 @@
           <t>مويه</t>
         </is>
       </c>
+      <c r="BG31" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6468,6 +6630,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG32" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6654,6 +6821,11 @@
           <t>مياه حنفيه لغسيل الاسماك</t>
         </is>
       </c>
+      <c r="BG33" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6840,6 +7012,11 @@
           <t>مياه حنفية لغسيل الاسماك</t>
         </is>
       </c>
+      <c r="BG34" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7036,6 +7213,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7222,6 +7404,11 @@
           <t>مياه حنفية لغسيل الاسماك</t>
         </is>
       </c>
+      <c r="BG36" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7418,6 +7605,11 @@
           <t>مياة حنفية لغسيل الاسماك</t>
         </is>
       </c>
+      <c r="BG37" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7604,6 +7796,11 @@
           <t>مياه حنفية لغسيل الاسماك</t>
         </is>
       </c>
+      <c r="BG38" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7800,6 +7997,11 @@
           <t>مياه حنفية لغسيل الاسماك</t>
         </is>
       </c>
+      <c r="BG39" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7986,6 +8188,11 @@
           <t>مياه حنفيه لغسيل الاسماك</t>
         </is>
       </c>
+      <c r="BG40" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8172,6 +8379,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG41" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8368,6 +8580,11 @@
           <t>مياه حنفية لغسيل الاسماك م.ك</t>
         </is>
       </c>
+      <c r="BG42" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -8554,6 +8771,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG43" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8750,6 +8972,11 @@
           <t>مياه حنفية لغسيل الادوات م.ك</t>
         </is>
       </c>
+      <c r="BG44" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8936,6 +9163,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG45" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -9122,6 +9354,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG46" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9305,6 +9542,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG47" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9491,6 +9733,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG48" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -9677,6 +9924,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG49" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -9863,6 +10115,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG50" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -10049,6 +10306,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG51" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -10235,6 +10497,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG52" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -10416,6 +10683,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG53" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -10597,6 +10869,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG54" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -10783,6 +11060,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG55" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -10979,6 +11261,11 @@
           <t>مياه حنفية لغسيل الادوات (م .ك)</t>
         </is>
       </c>
+      <c r="BG56" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -11165,6 +11452,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG57" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -11361,6 +11653,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG58" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -11547,6 +11844,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG59" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -11733,6 +12035,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG60" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -11919,6 +12226,11 @@
           <t>مياه غسيل حنفية (م.ك</t>
         </is>
       </c>
+      <c r="BG61" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -12085,6 +12397,11 @@
           <t>مياه غسيل حنفية (م.ك)</t>
         </is>
       </c>
+      <c r="BG62" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -12266,6 +12583,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG63" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -12442,6 +12764,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG64" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -12628,6 +12955,11 @@
           <t>مياه حنفية للغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG65" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -12814,6 +13146,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG66" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -13000,6 +13337,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG67" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -13186,6 +13528,11 @@
           <t>مياه حنفية للغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG68" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -13372,6 +13719,11 @@
           <t>مياة حنفية للغسيل ك</t>
         </is>
       </c>
+      <c r="BG69" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -13568,6 +13920,11 @@
           <t>مياه قلتر اعداد</t>
         </is>
       </c>
+      <c r="BG70" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -13764,6 +14121,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG71" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -13950,6 +14312,11 @@
           <t>مياه حنفية لغسيل الاسماك</t>
         </is>
       </c>
+      <c r="BG72" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -14136,6 +14503,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG73" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -14322,6 +14694,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG74" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -14518,6 +14895,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG75" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -14704,6 +15086,11 @@
           <t>مياة بير</t>
         </is>
       </c>
+      <c r="BH76" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -14890,6 +15277,11 @@
           <t>مياة حنفية غسيل الادوات</t>
         </is>
       </c>
+      <c r="BG77" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -15076,6 +15468,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG78" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -15262,6 +15659,11 @@
           <t>مياه حنفية غسيل الادوات</t>
         </is>
       </c>
+      <c r="BG79" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -15443,6 +15845,11 @@
           <t>مياه حنفيه لغسيل الادوات (م.ك)</t>
         </is>
       </c>
+      <c r="BG80" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -15629,6 +16036,11 @@
           <t>مياه معباة غسيل للعجانه</t>
         </is>
       </c>
+      <c r="BG81" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -15815,6 +16227,11 @@
           <t>مياة حنفية لغسيل الادوات[م.ك]</t>
         </is>
       </c>
+      <c r="BG82" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -16001,6 +16418,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG83" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -16187,6 +16609,11 @@
           <t>مياة غسيل عجانة</t>
         </is>
       </c>
+      <c r="BG84" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -16373,6 +16800,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG85" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -16559,6 +16991,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG86" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -16745,6 +17182,11 @@
           <t>مياه حنفيه لغسيل الادوات (م.ك)</t>
         </is>
       </c>
+      <c r="BG87" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -16931,6 +17373,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG88" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -17117,6 +17564,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG89" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -17303,6 +17755,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG90" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -17489,6 +17946,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG91" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -17675,6 +18137,11 @@
           <t>مياه غسيل الادوات</t>
         </is>
       </c>
+      <c r="BG92" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -17861,6 +18328,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG93" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -18047,6 +18519,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG94" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -18233,6 +18710,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG95" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -18419,6 +18901,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG96" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -18605,6 +19092,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG97" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -18791,6 +19283,11 @@
           <t>مياه غسيل</t>
         </is>
       </c>
+      <c r="BG98" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -18977,6 +19474,11 @@
           <t>مياه غسيل</t>
         </is>
       </c>
+      <c r="BG99" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -19163,6 +19665,11 @@
           <t>مياه حنفية غسيل</t>
         </is>
       </c>
+      <c r="BG100" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -19349,6 +19856,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG101" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19535,6 +20047,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG102" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19721,6 +20238,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG103" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -19907,6 +20429,11 @@
           <t>مياه حنفية لغسيل الارز</t>
         </is>
       </c>
+      <c r="BG104" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -20093,6 +20620,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG105" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -20279,6 +20811,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG106" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -20465,6 +21002,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG107" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -20651,6 +21193,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG108" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -20837,6 +21384,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG109" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -21023,6 +21575,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG110" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -21209,6 +21766,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG111" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -21395,6 +21957,11 @@
           <t>مياه حنفية لغسيل الأدوات (م.ك)</t>
         </is>
       </c>
+      <c r="BG112" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -21581,6 +22148,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG113" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -21767,6 +22339,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG114" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -21963,6 +22540,11 @@
           <t>مويه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG115" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -22149,6 +22731,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG116" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -22335,6 +22922,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG117" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -22521,6 +23113,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG118" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -22707,6 +23304,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG119" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -22893,6 +23495,11 @@
           <t>مياه غسيل حنفية للادوات</t>
         </is>
       </c>
+      <c r="BG120" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -23079,6 +23686,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG121" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -23275,6 +23887,11 @@
           <t>مياه حنفيه لغسيل الأدوام (م.ك)</t>
         </is>
       </c>
+      <c r="BG122" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -23426,6 +24043,11 @@
           <t>defaulted</t>
         </is>
       </c>
+      <c r="BH123" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -23612,6 +24234,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG124" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -23798,6 +24425,11 @@
           <t>مياه غسيل ادوات</t>
         </is>
       </c>
+      <c r="BG125" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -23979,6 +24611,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH126" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -24165,6 +24802,11 @@
           <t>مياه غسيل حنفية للادوات</t>
         </is>
       </c>
+      <c r="BG127" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -24351,6 +24993,11 @@
           <t>مياه غسيل حنفية للادوات</t>
         </is>
       </c>
+      <c r="BG128" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -24547,6 +25194,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG129" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -24728,6 +25380,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH130" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -24914,6 +25571,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG131" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -25095,6 +25757,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH132" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -25281,6 +25948,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG133" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -25467,6 +26139,11 @@
           <t>مياه حنفية المرحلة الثانية الرئيسية</t>
         </is>
       </c>
+      <c r="BH134" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -25653,6 +26330,11 @@
           <t>مياه خزان في اعلى المرحلة الثانية الرئيسية</t>
         </is>
       </c>
+      <c r="BH135" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -25839,6 +26521,11 @@
           <t>مياه خزان المرحلة الاولى</t>
         </is>
       </c>
+      <c r="BH136" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -26025,6 +26712,11 @@
           <t>مياه حنفية المرحلة الاولى الرئيسية قرب البوابة</t>
         </is>
       </c>
+      <c r="BH137" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -26211,6 +26903,11 @@
           <t>مياه حنفية المرحلة الثانية</t>
         </is>
       </c>
+      <c r="BH138" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -26362,6 +27059,11 @@
           <t>defaulted</t>
         </is>
       </c>
+      <c r="BH139" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -26558,6 +27260,11 @@
           <t>مياه حوض</t>
         </is>
       </c>
+      <c r="BG140" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -26754,6 +27461,11 @@
           <t>مياه حوض</t>
         </is>
       </c>
+      <c r="BG141" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -26950,6 +27662,11 @@
           <t>مياه حوض</t>
         </is>
       </c>
+      <c r="BG142" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -27146,6 +27863,11 @@
           <t>مياه حوض</t>
         </is>
       </c>
+      <c r="BG143" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -27342,6 +28064,11 @@
           <t>مياه حوض</t>
         </is>
       </c>
+      <c r="BG144" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -27538,6 +28265,11 @@
           <t>مياه حوض</t>
         </is>
       </c>
+      <c r="BG145" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -27734,6 +28466,11 @@
           <t>مياه حنفية</t>
         </is>
       </c>
+      <c r="BG146" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -27920,6 +28657,11 @@
           <t>مياه حنفية لغسيل الأدوات م-ك</t>
         </is>
       </c>
+      <c r="BG147" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -28106,6 +28848,11 @@
           <t>مياه حنفية لغسيل الأدوات</t>
         </is>
       </c>
+      <c r="BG148" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -28302,6 +29049,11 @@
           <t>مياه حنفية لغسيل الأدوات</t>
         </is>
       </c>
+      <c r="BH149" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -28488,6 +29240,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG150" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -28674,6 +29431,11 @@
           <t>مياه حنفية لغسيل الأدوات</t>
         </is>
       </c>
+      <c r="BG151" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -28860,6 +29622,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG152" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -29046,6 +29813,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG153" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -29232,6 +30004,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG154" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -29418,6 +30195,11 @@
           <t>42- مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG155" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -29604,6 +30386,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG156" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -29790,6 +30577,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG157" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -29976,6 +30768,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG158" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -30162,6 +30959,11 @@
           <t>41- مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG159" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -30348,6 +31150,11 @@
           <t>38- مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG160" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -30534,6 +31341,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG161" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -30720,6 +31532,11 @@
           <t>مياه حنفية لغسيل الأدوات</t>
         </is>
       </c>
+      <c r="BG162" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -30906,6 +31723,11 @@
           <t>مياه حنفية لغسيل الأدوات م-ك</t>
         </is>
       </c>
+      <c r="BG163" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -31092,6 +31914,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG164" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -31278,6 +32105,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG165" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -31464,6 +32296,11 @@
           <t>مياه حنفية لغسيل الادوات م.ك</t>
         </is>
       </c>
+      <c r="BG166" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -31650,6 +32487,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG167" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -31811,6 +32653,11 @@
           <t>defaulted</t>
         </is>
       </c>
+      <c r="BH168" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -31992,6 +32839,11 @@
           <t>موية حوض</t>
         </is>
       </c>
+      <c r="BG169" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -32173,6 +33025,11 @@
           <t>موية إضافة فيتامين</t>
         </is>
       </c>
+      <c r="BG170" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -32354,6 +33211,11 @@
           <t>موية حوض</t>
         </is>
       </c>
+      <c r="BG171" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -32535,6 +33397,11 @@
           <t>موية</t>
         </is>
       </c>
+      <c r="BG172" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -32716,6 +33583,11 @@
           <t>موية حوض</t>
         </is>
       </c>
+      <c r="BG173" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -32897,6 +33769,11 @@
           <t>موية حوض</t>
         </is>
       </c>
+      <c r="BG174" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -33083,6 +33960,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG175" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -33269,6 +34151,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG176" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -33455,6 +34342,11 @@
           <t>مياه غسيل الادوات</t>
         </is>
       </c>
+      <c r="BG177" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -33641,6 +34533,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG178" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -33827,6 +34724,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG179" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -34013,6 +34915,11 @@
           <t>مياة حنفيل لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG180" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -34209,6 +35116,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG181" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -34395,6 +35307,11 @@
           <t>مياه حنفية لغسيل الادوات م/ك</t>
         </is>
       </c>
+      <c r="BG182" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -34581,6 +35498,11 @@
           <t>مياه غسيل ادوات</t>
         </is>
       </c>
+      <c r="BG183" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -34767,6 +35689,11 @@
           <t>مياه حنفية للغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG184" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -34953,6 +35880,11 @@
           <t>مياه حنفية لغسيل الادوات م-ك</t>
         </is>
       </c>
+      <c r="BG185" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -35139,6 +36071,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG186" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -35325,6 +36262,11 @@
           <t>مياه غسيل ادوات</t>
         </is>
       </c>
+      <c r="BG187" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -35521,6 +36463,11 @@
           <t>مياه معباة للعصائر</t>
         </is>
       </c>
+      <c r="BG188" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -35707,6 +36654,11 @@
           <t>مياه حنفية لغسيل الادوات م-ك</t>
         </is>
       </c>
+      <c r="BG189" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -35893,6 +36845,11 @@
           <t>مياه حنفية لغسيل الأدوات</t>
         </is>
       </c>
+      <c r="BG190" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -36079,6 +37036,11 @@
           <t>مياه حنفية لغسيل الأدوات</t>
         </is>
       </c>
+      <c r="BG191" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -36265,6 +37227,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG192" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -36451,6 +37418,11 @@
           <t>مياه حنفية لغسيل الأدوات</t>
         </is>
       </c>
+      <c r="BG193" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -36637,6 +37609,11 @@
           <t>مياه حنفية لغسيل الأدوات</t>
         </is>
       </c>
+      <c r="BG194" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -36823,6 +37800,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG195" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -37009,6 +37991,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG196" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -37195,6 +38182,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG197" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -37381,6 +38373,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG198" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -37567,6 +38564,11 @@
           <t>مياه حنفية لغسيل الأدوات (م.ك)</t>
         </is>
       </c>
+      <c r="BG199" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -37753,6 +38755,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG200" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -37939,6 +38946,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG201" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -38135,6 +39147,11 @@
           <t>مويه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG202" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -38321,6 +39338,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG203" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -38507,6 +39529,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG204" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -38693,6 +39720,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG205" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -38879,6 +39911,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG206" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -39065,6 +40102,11 @@
           <t>مياه غسيل حنفية للادوات</t>
         </is>
       </c>
+      <c r="BG207" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -39251,6 +40293,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG208" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -39447,6 +40494,11 @@
           <t>مياه حنفيه لغسيل الأدوام (م.ك)</t>
         </is>
       </c>
+      <c r="BG209" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -39598,6 +40650,11 @@
           <t>defaulted</t>
         </is>
       </c>
+      <c r="BH210" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -39784,6 +40841,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG211" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -39970,6 +41032,11 @@
           <t>مياه غسيل ادوات</t>
         </is>
       </c>
+      <c r="BG212" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -40151,6 +41218,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH213" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -40337,6 +41409,11 @@
           <t>مياه غسيل حنفية للادوات</t>
         </is>
       </c>
+      <c r="BG214" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -40523,6 +41600,11 @@
           <t>مياه غسيل حنفية للادوات</t>
         </is>
       </c>
+      <c r="BG215" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -40719,6 +41801,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG216" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -40900,6 +41987,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH217" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -41086,6 +42178,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG218" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -41267,6 +42364,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH219" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -41453,6 +42555,11 @@
           <t>مياه غسيل ادوات</t>
         </is>
       </c>
+      <c r="BG220" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -41639,6 +42746,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG221" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -41825,6 +42937,11 @@
           <t>مياه غسيل ادوات</t>
         </is>
       </c>
+      <c r="BG222" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -42016,6 +43133,11 @@
           <t>مياه غسيل ادوات كيمياء</t>
         </is>
       </c>
+      <c r="BG223" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -42202,6 +43324,11 @@
           <t>مياه حنفية لغسيل الادوات (ك)</t>
         </is>
       </c>
+      <c r="BG224" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -42388,6 +43515,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG225" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -42574,6 +43706,11 @@
           <t>مياه حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG226" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -42760,6 +43897,11 @@
           <t>مياه غسيل ادوات</t>
         </is>
       </c>
+      <c r="BG227" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -42946,6 +44088,11 @@
           <t>مياة حنفية لغسيل المواشي</t>
         </is>
       </c>
+      <c r="BG228" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -43132,6 +44279,11 @@
           <t>مياه غسيل ادوات ك</t>
         </is>
       </c>
+      <c r="BG229" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -43318,6 +44470,11 @@
           <t>مياه غسيل ادوات ك</t>
         </is>
       </c>
+      <c r="BG230" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -43504,6 +44661,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG231" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -43690,6 +44852,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG232" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -43876,6 +45043,11 @@
           <t>مياة حنفية لغسيل الادوات م.ك</t>
         </is>
       </c>
+      <c r="BG233" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -44062,6 +45234,11 @@
           <t>مياة حنفية لغسيل الادوات م.ك(المخبز)</t>
         </is>
       </c>
+      <c r="BG234" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -44258,6 +45435,11 @@
           <t>مياه مجهولة المصدر</t>
         </is>
       </c>
+      <c r="BH235" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -44444,6 +45626,11 @@
           <t>مياة غسل اللحم م-ك</t>
         </is>
       </c>
+      <c r="BG236" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -44630,6 +45817,11 @@
           <t>مياه حنفية لغسيل الادوات م-ك</t>
         </is>
       </c>
+      <c r="BG237" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -44816,6 +46008,11 @@
           <t>مياه حنفية لغسيل الأدوات</t>
         </is>
       </c>
+      <c r="BG238" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -45002,6 +46199,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG239" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -45188,6 +46390,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG240" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -45364,6 +46571,11 @@
           <t>مياة حنفية لغسيل الادوات م- ك</t>
         </is>
       </c>
+      <c r="BG241" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -45545,6 +46757,11 @@
           <t>مياه حنفية للغسيل</t>
         </is>
       </c>
+      <c r="BG242" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -45731,6 +46948,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG243" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -45912,6 +47134,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG244" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -46108,6 +47335,11 @@
           <t>مياة لغسيل الادوات م-ك</t>
         </is>
       </c>
+      <c r="BG245" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -46295,6 +47527,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG246" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -46481,6 +47718,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG247" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -46667,6 +47909,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG248" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -46853,6 +48100,11 @@
           <t>مياة رقم 1 من خزان المرحلة الثالثة م-ك</t>
         </is>
       </c>
+      <c r="BH249" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -47039,6 +48291,11 @@
           <t>مياة رقم 2 الخزان الاحتياطي للمرحلة الثالثه م-ك</t>
         </is>
       </c>
+      <c r="BH250" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -47225,6 +48482,11 @@
           <t>مياة 3 الخزان الرائيسي للمرحلة الرابعة م-ك</t>
         </is>
       </c>
+      <c r="BH251" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -47401,6 +48663,11 @@
           <t>مياة للعجانة 1 م- ك</t>
         </is>
       </c>
+      <c r="BG252" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -47577,6 +48844,11 @@
           <t>مياة للعجانه 2 م-ك</t>
         </is>
       </c>
+      <c r="BG253" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -47753,6 +49025,11 @@
           <t>مياه غسيل أدوات</t>
         </is>
       </c>
+      <c r="BG254" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -47929,6 +49206,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG255" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -48115,6 +49397,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG256" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -48301,6 +49588,11 @@
           <t>مياة معبأة للعجانه م- ك</t>
         </is>
       </c>
+      <c r="BG257" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -48487,6 +49779,11 @@
           <t>مياة معبأة للعجانه م- ك</t>
         </is>
       </c>
+      <c r="BG258" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -48673,6 +49970,11 @@
           <t>مياة لغسيل الادوات م- ك</t>
         </is>
       </c>
+      <c r="BG259" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -48824,6 +50126,11 @@
           <t>مياه الحنفية</t>
         </is>
       </c>
+      <c r="BH260" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -49010,6 +50317,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG261" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -49186,6 +50498,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH262" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -49372,6 +50689,11 @@
           <t>مياه غسيل أدوات لجميع الفروع</t>
         </is>
       </c>
+      <c r="BG263" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -49558,6 +50880,11 @@
           <t>مياه غسيل أرضيات</t>
         </is>
       </c>
+      <c r="BG264" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -49744,6 +51071,11 @@
           <t>مياة لتغسيل الادوات م ك</t>
         </is>
       </c>
+      <c r="BG265" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -49930,6 +51262,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG266" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -50116,6 +51453,11 @@
           <t>مياة لغسيل الادوات م ك</t>
         </is>
       </c>
+      <c r="BG267" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -50302,6 +51644,11 @@
           <t>مياة لغسيل الادوات م- ك</t>
         </is>
       </c>
+      <c r="BG268" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -50488,6 +51835,11 @@
           <t>مياة لغسيل الادوات م - ك</t>
         </is>
       </c>
+      <c r="BG269" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -50674,6 +52026,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG270" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -50860,6 +52217,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG271" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -51046,6 +52408,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG272" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -51232,6 +52599,11 @@
           <t>مياه لغسيل الأدوات م-ك</t>
         </is>
       </c>
+      <c r="BG273" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -51418,6 +52790,11 @@
           <t>خزان الوحدة الرئيسية خاصه ح</t>
         </is>
       </c>
+      <c r="BH274" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -51604,6 +52981,11 @@
           <t>خزان مرحلة رقم 2 المطبخ خاصة ح</t>
         </is>
       </c>
+      <c r="BH275" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -51790,6 +53172,11 @@
           <t>خزان مرحلة رقم 3 خلف المسجد خاصه ح</t>
         </is>
       </c>
+      <c r="BH276" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -51976,6 +53363,11 @@
           <t>مياه حنفيه الشؤون الفنية خاصة ح</t>
         </is>
       </c>
+      <c r="BH277" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -52162,6 +53554,11 @@
           <t>مياه حنفيه الشؤون الفنية خاصة ص</t>
         </is>
       </c>
+      <c r="BH278" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -52348,6 +53745,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH279" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -52534,6 +53936,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH280" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -52720,6 +54127,11 @@
           <t>مياه لغسيل الأدوات ك -م</t>
         </is>
       </c>
+      <c r="BG281" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -52916,6 +54328,11 @@
           <t>مياه خاصة م، ع، 7 (م.ك)</t>
         </is>
       </c>
+      <c r="BH282" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -53102,6 +54519,11 @@
           <t>مياه خاصة غسيل المستوصف م، م (م.ك)</t>
         </is>
       </c>
+      <c r="BH283" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -53298,6 +54720,11 @@
           <t>مياه خاصة الشؤون الفنية م (م.ك)</t>
         </is>
       </c>
+      <c r="BH284" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -53494,6 +54921,11 @@
           <t>مياه خاصة خزان المرحلة الاولى م (م.ك)</t>
         </is>
       </c>
+      <c r="BH285" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -53690,6 +55122,11 @@
           <t>مياه خاصة خزان الاحتياطي م (م.ك)</t>
         </is>
       </c>
+      <c r="BH286" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -53886,6 +55323,11 @@
           <t>مياه خاصة لغسيل الرز م (م.ك)</t>
         </is>
       </c>
+      <c r="BH287" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -54082,6 +55524,11 @@
           <t>مياه خاصة حنفية للطبخ م (م.ك)</t>
         </is>
       </c>
+      <c r="BH288" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -54268,6 +55715,11 @@
           <t>مياه خاصة شرب هنا م (م.ك)</t>
         </is>
       </c>
+      <c r="BH289" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -54454,6 +55906,11 @@
           <t>مياه خاصة خزان اساسي مرحلة اولى ن (م.ك)</t>
         </is>
       </c>
+      <c r="BH290" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -54640,6 +56097,11 @@
           <t>مياه خاصة حنفية للطبخ ن (م.ك)</t>
         </is>
       </c>
+      <c r="BH291" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -54826,6 +56288,11 @@
           <t>مياه خاصة حنفية لغسيل الخضار والفواكه ن (م.ك)</t>
         </is>
       </c>
+      <c r="BH292" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -55012,6 +56479,11 @@
           <t>مياه خاصة لدورات المياه ن، ع، ج2، 4 (م.ك)</t>
         </is>
       </c>
+      <c r="BH293" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -55198,6 +56670,11 @@
           <t>مياه خاصة خزان اساسي مرحلة اولى ف (م.ك)</t>
         </is>
       </c>
+      <c r="BH294" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -55384,6 +56861,11 @@
           <t>مياه خاصة ج2، ف (م.ك)</t>
         </is>
       </c>
+      <c r="BH295" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -55570,6 +57052,11 @@
           <t>مياه خاصة شرطة عسكرية ج2، ف (م.ك)</t>
         </is>
       </c>
+      <c r="BH296" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -55756,6 +57243,11 @@
           <t>مياه خاصة حنفية للطبخ ف (م.ك)</t>
         </is>
       </c>
+      <c r="BH297" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -55942,6 +57434,11 @@
           <t>مياه خاصة حنفية لغسيل الخضار ف (م.ك)</t>
         </is>
       </c>
+      <c r="BH298" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -56128,6 +57625,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG299" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -56314,6 +57816,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG300" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -56500,6 +58007,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG301" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -56691,6 +58203,11 @@
           <t>مياه حنفية مبنى الاداره خاصة ع</t>
         </is>
       </c>
+      <c r="BH302" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -56882,6 +58399,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH303" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -57063,6 +58585,11 @@
           <t>مياه حنفية ع 22 خاصة ع</t>
         </is>
       </c>
+      <c r="BH304" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -57244,6 +58771,11 @@
           <t>مياه خزان رئيسي خاصة ع</t>
         </is>
       </c>
+      <c r="BH305" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -57425,6 +58957,11 @@
           <t>مياه طبخ خاصة ع</t>
         </is>
       </c>
+      <c r="BH306" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -57606,6 +59143,11 @@
           <t>مياه غسيل الدجاج خاصة ع</t>
         </is>
       </c>
+      <c r="BH307" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -57792,6 +59334,11 @@
           <t>مياه لغسيل الادوات م-ك</t>
         </is>
       </c>
+      <c r="BG308" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -57958,6 +59505,11 @@
           <t>مياه خاصة حنفية خزان احتياط ن ، ن</t>
         </is>
       </c>
+      <c r="BG309" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -58124,6 +59676,11 @@
           <t>مياه خاصة خزان رئيسي ن ، ن</t>
         </is>
       </c>
+      <c r="BG310" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -58290,6 +59847,11 @@
           <t>مياه خاصة حنفية غسيل ع5 ، ن ، ن</t>
         </is>
       </c>
+      <c r="BG311" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -58456,6 +60018,11 @@
           <t>مياه خاصة حنفية غسيل ع4 ، ن ، ن</t>
         </is>
       </c>
+      <c r="BG312" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -58622,6 +60189,11 @@
           <t>مياه خاصة حنفية مطبخ الادارة ن ، ن</t>
         </is>
       </c>
+      <c r="BG313" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -58788,6 +60360,11 @@
           <t>مياه خاصة حنفية للغسيل مكتب ح ، ن ، ن</t>
         </is>
       </c>
+      <c r="BG314" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -58959,6 +60536,11 @@
           <t>مياه خاصة خزان احتياط ع ، ش</t>
         </is>
       </c>
+      <c r="BH315" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -59130,6 +60712,11 @@
           <t>مياه خاصة حنفية للغسيل ج1 ، ع ، ش</t>
         </is>
       </c>
+      <c r="BH316" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -59301,6 +60888,11 @@
           <t>مياه خاصة حنفية للغسيل ج4 ، ع ، ش</t>
         </is>
       </c>
+      <c r="BH317" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -59472,6 +61064,11 @@
           <t>مياه خاصة حنفية للغسيل وحدة صحية ع ، ش</t>
         </is>
       </c>
+      <c r="BH318" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -59643,6 +61240,11 @@
           <t>مياه خاصة حنفية للغسيل مكتبة ع ، ش</t>
         </is>
       </c>
+      <c r="BH319" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -59814,6 +61416,11 @@
           <t>مياه خاصة حنفية للغسيل مطبخ مبنى الادارة ع ، ش</t>
         </is>
       </c>
+      <c r="BH320" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -59985,6 +61592,11 @@
           <t>مياه خاصة حنفية للغسيل دورة مياه مبنى الادارة ع ، ش</t>
         </is>
       </c>
+      <c r="BH321" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -60175,6 +61787,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG322" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -60355,6 +61972,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG323" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -60535,6 +62157,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG324" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -60715,6 +62342,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG325" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -60895,6 +62527,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG326" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -61075,6 +62712,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG327" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -61255,6 +62897,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG328" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -61435,6 +63082,11 @@
           <t>مياه غسيل أدوات م - ك</t>
         </is>
       </c>
+      <c r="BG329" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -61625,6 +63277,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG330" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -61810,6 +63467,11 @@
           <t>مياة غسيل ادوات م ك</t>
         </is>
       </c>
+      <c r="BG331" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -61990,6 +63652,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG332" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -62175,6 +63842,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG333" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -62365,6 +64037,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG334" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -62545,6 +64222,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG335" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -62720,6 +64402,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG336" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -62900,6 +64587,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG337" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -63080,6 +64772,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG338" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -63260,6 +64957,11 @@
           <t>مياه غسيل أدوات م-ك</t>
         </is>
       </c>
+      <c r="BG339" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -63440,6 +65142,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG340" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -63620,6 +65327,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG341" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -63800,6 +65512,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG342" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -63975,6 +65692,11 @@
           <t>مياة غسيل ادوات م-ك</t>
         </is>
       </c>
+      <c r="BG343" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -64150,6 +65872,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG344" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -64305,6 +66032,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH345" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -64460,6 +66192,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH346" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -64615,6 +66352,11 @@
           <t>مياه لغسيل الأدوات رقمها (49)</t>
         </is>
       </c>
+      <c r="BH347" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -64770,6 +66512,11 @@
           <t>مياه لغسيل الأدوات رقمها (7)</t>
         </is>
       </c>
+      <c r="BH348" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -64960,6 +66707,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG349" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -65140,6 +66892,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG350" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -65315,6 +67072,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG351" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -65490,6 +67252,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG352" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -65670,6 +67437,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG353" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -65815,6 +67587,11 @@
           <t>defaulted</t>
         </is>
       </c>
+      <c r="BH354" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -65990,6 +67767,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG355" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -66150,6 +67932,11 @@
           <t>مياه متحركة</t>
         </is>
       </c>
+      <c r="BG356" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -66310,6 +68097,11 @@
           <t>مياه راكده</t>
         </is>
       </c>
+      <c r="BG357" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -66485,9 +68277,14 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG358" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BF358"/>
+  <autoFilter ref="A1:BH358"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -66498,7 +68295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -66524,7 +68321,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Columns: 58</t>
+          <t>Columns: 60</t>
         </is>
       </c>
     </row>
@@ -67571,6 +69368,42 @@
       <c r="D63" t="inlineStr">
         <is>
           <t>مياة حنفية للغسيل | مياة غسيل حنفية | مياة حنفية لغسيل الادوات</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>292</v>
+      </c>
+      <c r="C64" t="n">
+        <v>65</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب | فرع أمانة في الغرب | فرع أمانة في الغرب</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>sector_flag</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>65</v>
+      </c>
+      <c r="C65" t="n">
+        <v>292</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>private | no_municipality | no_municipality</t>
         </is>
       </c>
     </row>

--- a/clean/chemistry/chem_water_analysis_2025.xlsx
+++ b/clean/chemistry/chem_water_analysis_2025.xlsx
@@ -24038,11 +24038,6 @@
           <t>مياه الحنفية</t>
         </is>
       </c>
-      <c r="BE123" t="inlineStr">
-        <is>
-          <t>defaulted</t>
-        </is>
-      </c>
       <c r="BH123" t="inlineStr">
         <is>
           <t>no_municipality</t>
@@ -27054,11 +27049,6 @@
           <t>مياه الحنفية</t>
         </is>
       </c>
-      <c r="BE139" t="inlineStr">
-        <is>
-          <t>defaulted</t>
-        </is>
-      </c>
       <c r="BH139" t="inlineStr">
         <is>
           <t>no_municipality</t>
@@ -27252,7 +27242,7 @@
       </c>
       <c r="BD140" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه غير صالحة للشرب</t>
         </is>
       </c>
       <c r="BF140" t="inlineStr">
@@ -27453,7 +27443,7 @@
       </c>
       <c r="BD141" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه غير صالحة للشرب</t>
         </is>
       </c>
       <c r="BF141" t="inlineStr">
@@ -27654,7 +27644,7 @@
       </c>
       <c r="BD142" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه غير صالحة للشرب</t>
         </is>
       </c>
       <c r="BF142" t="inlineStr">
@@ -27855,7 +27845,7 @@
       </c>
       <c r="BD143" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه غير صالحة للشرب</t>
         </is>
       </c>
       <c r="BF143" t="inlineStr">
@@ -28056,7 +28046,7 @@
       </c>
       <c r="BD144" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه غير صالحة للشرب</t>
         </is>
       </c>
       <c r="BF144" t="inlineStr">
@@ -28257,7 +28247,7 @@
       </c>
       <c r="BD145" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه غير صالحة للشرب</t>
         </is>
       </c>
       <c r="BF145" t="inlineStr">
@@ -32648,11 +32638,6 @@
           <t>مياه الحنفية</t>
         </is>
       </c>
-      <c r="BE168" t="inlineStr">
-        <is>
-          <t>defaulted</t>
-        </is>
-      </c>
       <c r="BH168" t="inlineStr">
         <is>
           <t>no_municipality</t>
@@ -32831,7 +32816,7 @@
       </c>
       <c r="BD169" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه غير صالحة للشرب</t>
         </is>
       </c>
       <c r="BF169" t="inlineStr">
@@ -33203,7 +33188,7 @@
       </c>
       <c r="BD171" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه غير صالحة للشرب</t>
         </is>
       </c>
       <c r="BF171" t="inlineStr">
@@ -33575,7 +33560,7 @@
       </c>
       <c r="BD173" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه غير صالحة للشرب</t>
         </is>
       </c>
       <c r="BF173" t="inlineStr">
@@ -33761,7 +33746,7 @@
       </c>
       <c r="BD174" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه غير صالحة للشرب</t>
         </is>
       </c>
       <c r="BF174" t="inlineStr">
@@ -40645,11 +40630,6 @@
           <t>مياه الحنفية</t>
         </is>
       </c>
-      <c r="BE210" t="inlineStr">
-        <is>
-          <t>defaulted</t>
-        </is>
-      </c>
       <c r="BH210" t="inlineStr">
         <is>
           <t>no_municipality</t>
@@ -43123,11 +43103,6 @@
           <t>مياه الحنفية</t>
         </is>
       </c>
-      <c r="BE223" t="inlineStr">
-        <is>
-          <t>reclassified</t>
-        </is>
-      </c>
       <c r="BF223" t="inlineStr">
         <is>
           <t>مياه غسيل ادوات كيمياء</t>
@@ -49771,7 +49746,7 @@
       </c>
       <c r="BD258" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF258" t="inlineStr">
@@ -67582,11 +67557,6 @@
           <t>مياه الحنفية</t>
         </is>
       </c>
-      <c r="BE354" t="inlineStr">
-        <is>
-          <t>defaulted</t>
-        </is>
-      </c>
       <c r="BH354" t="inlineStr">
         <is>
           <t>no_municipality</t>
@@ -67924,7 +67894,7 @@
       </c>
       <c r="BD356" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه غير صالحة للشرب</t>
         </is>
       </c>
       <c r="BF356" t="inlineStr">
@@ -68089,7 +68059,7 @@
       </c>
       <c r="BD357" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه غير صالحة للشرب</t>
         </is>
       </c>
       <c r="BF357" t="inlineStr">
@@ -69342,16 +69312,12 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>351</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>defaulted | defaulted | defaulted</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">

--- a/clean/chemistry/chem_water_analysis_2025.xlsx
+++ b/clean/chemistry/chem_water_analysis_2025.xlsx
@@ -7788,7 +7788,7 @@
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="BD40" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF40" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="BD41" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF41" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF52" t="inlineStr">
@@ -36440,7 +36440,7 @@
       </c>
       <c r="BD188" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF188" t="inlineStr">
@@ -37586,7 +37586,7 @@
       </c>
       <c r="BD194" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF194" t="inlineStr">
@@ -53712,7 +53712,7 @@
       </c>
       <c r="BD279" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF279" t="inlineStr">
@@ -53903,7 +53903,7 @@
       </c>
       <c r="BD280" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF280" t="inlineStr">

--- a/clean/chemistry/chem_water_analysis_2025.xlsx
+++ b/clean/chemistry/chem_water_analysis_2025.xlsx
@@ -7788,7 +7788,7 @@
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه الحنفية</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه الحنفية</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="BD40" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه الحنفية</t>
         </is>
       </c>
       <c r="BF40" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="BD41" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه الحنفية</t>
         </is>
       </c>
       <c r="BF41" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه الحنفية</t>
         </is>
       </c>
       <c r="BF52" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="BD76" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه الحنفية</t>
         </is>
       </c>
       <c r="BF76" t="inlineStr">
@@ -37586,7 +37586,7 @@
       </c>
       <c r="BD194" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه الحنفية</t>
         </is>
       </c>
       <c r="BF194" t="inlineStr">
@@ -49746,7 +49746,7 @@
       </c>
       <c r="BD258" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه الحنفية</t>
         </is>
       </c>
       <c r="BF258" t="inlineStr">
@@ -53712,7 +53712,7 @@
       </c>
       <c r="BD279" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه الحنفية</t>
         </is>
       </c>
       <c r="BF279" t="inlineStr">
@@ -53903,7 +53903,7 @@
       </c>
       <c r="BD280" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه الحنفية</t>
         </is>
       </c>
       <c r="BF280" t="inlineStr">

--- a/clean/chemistry/chem_water_analysis_2025.xlsx
+++ b/clean/chemistry/chem_water_analysis_2025.xlsx
@@ -975,7 +975,7 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="BD40" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF40" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="BD41" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF41" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF42" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF45" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="BD47" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF47" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="BD48" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF48" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF51" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF52" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF54" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF55" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="BD58" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF58" t="inlineStr">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="BD59" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF59" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="BD60" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF60" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="BD61" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF61" t="inlineStr">
@@ -12389,7 +12389,7 @@
       </c>
       <c r="BD62" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
@@ -12575,7 +12575,7 @@
       </c>
       <c r="BD63" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF63" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="BD65" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF65" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="BD66" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF66" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="BD67" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF67" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="BD68" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF68" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="BD70" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF70" t="inlineStr">
@@ -14113,7 +14113,7 @@
       </c>
       <c r="BD71" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF71" t="inlineStr">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="BD72" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF72" t="inlineStr">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF73" t="inlineStr">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="BD74" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF74" t="inlineStr">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="BD75" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF75" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="BD76" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF76" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
@@ -15460,7 +15460,7 @@
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF79" t="inlineStr">
@@ -15837,7 +15837,7 @@
       </c>
       <c r="BD80" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF80" t="inlineStr">
@@ -16028,7 +16028,7 @@
       </c>
       <c r="BD81" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF81" t="inlineStr">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="BD82" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF82" t="inlineStr">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="BD83" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF83" t="inlineStr">
@@ -16601,7 +16601,7 @@
       </c>
       <c r="BD84" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF84" t="inlineStr">
@@ -16792,7 +16792,7 @@
       </c>
       <c r="BD85" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF85" t="inlineStr">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="BD86" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF86" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="BD87" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF87" t="inlineStr">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="BD89" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF89" t="inlineStr">
@@ -17747,7 +17747,7 @@
       </c>
       <c r="BD90" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF90" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="BD91" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF91" t="inlineStr">
@@ -18129,7 +18129,7 @@
       </c>
       <c r="BD92" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF92" t="inlineStr">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="BD93" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF93" t="inlineStr">
@@ -18511,7 +18511,7 @@
       </c>
       <c r="BD94" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF94" t="inlineStr">
@@ -18702,7 +18702,7 @@
       </c>
       <c r="BD95" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF95" t="inlineStr">
@@ -18893,7 +18893,7 @@
       </c>
       <c r="BD96" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF96" t="inlineStr">
@@ -19084,7 +19084,7 @@
       </c>
       <c r="BD97" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF97" t="inlineStr">
@@ -19275,7 +19275,7 @@
       </c>
       <c r="BD98" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF98" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="BD99" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF99" t="inlineStr">
@@ -19657,7 +19657,7 @@
       </c>
       <c r="BD100" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF100" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="BD101" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF101" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="BD102" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF102" t="inlineStr">
@@ -20230,7 +20230,7 @@
       </c>
       <c r="BD103" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF103" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
@@ -20612,7 +20612,7 @@
       </c>
       <c r="BD105" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF105" t="inlineStr">
@@ -20803,7 +20803,7 @@
       </c>
       <c r="BD106" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF106" t="inlineStr">
@@ -20994,7 +20994,7 @@
       </c>
       <c r="BD107" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF107" t="inlineStr">
@@ -21185,7 +21185,7 @@
       </c>
       <c r="BD108" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF108" t="inlineStr">
@@ -21376,7 +21376,7 @@
       </c>
       <c r="BD109" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF109" t="inlineStr">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="BD110" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF110" t="inlineStr">
@@ -21758,7 +21758,7 @@
       </c>
       <c r="BD111" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF111" t="inlineStr">
@@ -21949,7 +21949,7 @@
       </c>
       <c r="BD112" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF112" t="inlineStr">
@@ -22140,7 +22140,7 @@
       </c>
       <c r="BD113" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF113" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="BD114" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF114" t="inlineStr">
@@ -22532,7 +22532,7 @@
       </c>
       <c r="BD115" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF115" t="inlineStr">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="BD116" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF116" t="inlineStr">
@@ -22914,7 +22914,7 @@
       </c>
       <c r="BD117" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF117" t="inlineStr">
@@ -23105,7 +23105,7 @@
       </c>
       <c r="BD118" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF118" t="inlineStr">
@@ -23296,7 +23296,7 @@
       </c>
       <c r="BD119" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF119" t="inlineStr">
@@ -23487,7 +23487,7 @@
       </c>
       <c r="BD120" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF120" t="inlineStr">
@@ -23678,7 +23678,7 @@
       </c>
       <c r="BD121" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF121" t="inlineStr">
@@ -23879,7 +23879,7 @@
       </c>
       <c r="BD122" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF122" t="inlineStr">
@@ -24035,7 +24035,7 @@
       </c>
       <c r="BD123" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BH123" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="BD124" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF124" t="inlineStr">
@@ -24412,7 +24412,7 @@
       </c>
       <c r="BD125" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF125" t="inlineStr">
@@ -24598,7 +24598,7 @@
       </c>
       <c r="BD126" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF126" t="inlineStr">
@@ -24789,7 +24789,7 @@
       </c>
       <c r="BD127" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF127" t="inlineStr">
@@ -24980,7 +24980,7 @@
       </c>
       <c r="BD128" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF128" t="inlineStr">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="BD129" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF129" t="inlineStr">
@@ -25367,7 +25367,7 @@
       </c>
       <c r="BD130" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF130" t="inlineStr">
@@ -25558,7 +25558,7 @@
       </c>
       <c r="BD131" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF131" t="inlineStr">
@@ -25744,7 +25744,7 @@
       </c>
       <c r="BD132" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF132" t="inlineStr">
@@ -25935,7 +25935,7 @@
       </c>
       <c r="BD133" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF133" t="inlineStr">
@@ -26126,7 +26126,7 @@
       </c>
       <c r="BD134" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF134" t="inlineStr">
@@ -26317,7 +26317,7 @@
       </c>
       <c r="BD135" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF135" t="inlineStr">
@@ -26508,7 +26508,7 @@
       </c>
       <c r="BD136" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF136" t="inlineStr">
@@ -26699,7 +26699,7 @@
       </c>
       <c r="BD137" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF137" t="inlineStr">
@@ -26890,7 +26890,7 @@
       </c>
       <c r="BD138" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF138" t="inlineStr">
@@ -27046,7 +27046,7 @@
       </c>
       <c r="BD139" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BH139" t="inlineStr">
@@ -28448,7 +28448,7 @@
       </c>
       <c r="BD146" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF146" t="inlineStr">
@@ -28639,7 +28639,7 @@
       </c>
       <c r="BD147" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF147" t="inlineStr">
@@ -28830,7 +28830,7 @@
       </c>
       <c r="BD148" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF148" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="BD149" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF149" t="inlineStr">
@@ -29222,7 +29222,7 @@
       </c>
       <c r="BD150" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF150" t="inlineStr">
@@ -29413,7 +29413,7 @@
       </c>
       <c r="BD151" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF151" t="inlineStr">
@@ -29604,7 +29604,7 @@
       </c>
       <c r="BD152" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF152" t="inlineStr">
@@ -29795,7 +29795,7 @@
       </c>
       <c r="BD153" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF153" t="inlineStr">
@@ -29986,7 +29986,7 @@
       </c>
       <c r="BD154" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF154" t="inlineStr">
@@ -30177,7 +30177,7 @@
       </c>
       <c r="BD155" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF155" t="inlineStr">
@@ -30368,7 +30368,7 @@
       </c>
       <c r="BD156" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF156" t="inlineStr">
@@ -30559,7 +30559,7 @@
       </c>
       <c r="BD157" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF157" t="inlineStr">
@@ -30750,7 +30750,7 @@
       </c>
       <c r="BD158" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF158" t="inlineStr">
@@ -30941,7 +30941,7 @@
       </c>
       <c r="BD159" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF159" t="inlineStr">
@@ -31132,7 +31132,7 @@
       </c>
       <c r="BD160" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF160" t="inlineStr">
@@ -31323,7 +31323,7 @@
       </c>
       <c r="BD161" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF161" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="BD162" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF162" t="inlineStr">
@@ -31705,7 +31705,7 @@
       </c>
       <c r="BD163" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF163" t="inlineStr">
@@ -31896,7 +31896,7 @@
       </c>
       <c r="BD164" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF164" t="inlineStr">
@@ -32087,7 +32087,7 @@
       </c>
       <c r="BD165" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF165" t="inlineStr">
@@ -32278,7 +32278,7 @@
       </c>
       <c r="BD166" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF166" t="inlineStr">
@@ -32469,7 +32469,7 @@
       </c>
       <c r="BD167" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF167" t="inlineStr">
@@ -32635,7 +32635,7 @@
       </c>
       <c r="BD168" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BH168" t="inlineStr">
@@ -33002,7 +33002,7 @@
       </c>
       <c r="BD170" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF170" t="inlineStr">
@@ -33374,7 +33374,7 @@
       </c>
       <c r="BD172" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF172" t="inlineStr">
@@ -33937,7 +33937,7 @@
       </c>
       <c r="BD175" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF175" t="inlineStr">
@@ -34128,7 +34128,7 @@
       </c>
       <c r="BD176" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF176" t="inlineStr">
@@ -34319,7 +34319,7 @@
       </c>
       <c r="BD177" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF177" t="inlineStr">
@@ -34510,7 +34510,7 @@
       </c>
       <c r="BD178" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF178" t="inlineStr">
@@ -34701,7 +34701,7 @@
       </c>
       <c r="BD179" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF179" t="inlineStr">
@@ -34892,7 +34892,7 @@
       </c>
       <c r="BD180" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF180" t="inlineStr">
@@ -35093,7 +35093,7 @@
       </c>
       <c r="BD181" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF181" t="inlineStr">
@@ -35284,7 +35284,7 @@
       </c>
       <c r="BD182" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF182" t="inlineStr">
@@ -35475,7 +35475,7 @@
       </c>
       <c r="BD183" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF183" t="inlineStr">
@@ -35666,7 +35666,7 @@
       </c>
       <c r="BD184" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF184" t="inlineStr">
@@ -35857,7 +35857,7 @@
       </c>
       <c r="BD185" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF185" t="inlineStr">
@@ -36048,7 +36048,7 @@
       </c>
       <c r="BD186" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF186" t="inlineStr">
@@ -36239,7 +36239,7 @@
       </c>
       <c r="BD187" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF187" t="inlineStr">
@@ -36440,7 +36440,7 @@
       </c>
       <c r="BD188" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF188" t="inlineStr">
@@ -36631,7 +36631,7 @@
       </c>
       <c r="BD189" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF189" t="inlineStr">
@@ -36822,7 +36822,7 @@
       </c>
       <c r="BD190" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF190" t="inlineStr">
@@ -37013,7 +37013,7 @@
       </c>
       <c r="BD191" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF191" t="inlineStr">
@@ -37204,7 +37204,7 @@
       </c>
       <c r="BD192" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF192" t="inlineStr">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="BD193" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF193" t="inlineStr">
@@ -37586,7 +37586,7 @@
       </c>
       <c r="BD194" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF194" t="inlineStr">
@@ -37777,7 +37777,7 @@
       </c>
       <c r="BD195" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF195" t="inlineStr">
@@ -37968,7 +37968,7 @@
       </c>
       <c r="BD196" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF196" t="inlineStr">
@@ -38159,7 +38159,7 @@
       </c>
       <c r="BD197" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF197" t="inlineStr">
@@ -38350,7 +38350,7 @@
       </c>
       <c r="BD198" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF198" t="inlineStr">
@@ -38541,7 +38541,7 @@
       </c>
       <c r="BD199" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF199" t="inlineStr">
@@ -38732,7 +38732,7 @@
       </c>
       <c r="BD200" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF200" t="inlineStr">
@@ -38923,7 +38923,7 @@
       </c>
       <c r="BD201" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF201" t="inlineStr">
@@ -39124,7 +39124,7 @@
       </c>
       <c r="BD202" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF202" t="inlineStr">
@@ -39315,7 +39315,7 @@
       </c>
       <c r="BD203" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF203" t="inlineStr">
@@ -39506,7 +39506,7 @@
       </c>
       <c r="BD204" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF204" t="inlineStr">
@@ -39697,7 +39697,7 @@
       </c>
       <c r="BD205" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF205" t="inlineStr">
@@ -39888,7 +39888,7 @@
       </c>
       <c r="BD206" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF206" t="inlineStr">
@@ -40079,7 +40079,7 @@
       </c>
       <c r="BD207" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF207" t="inlineStr">
@@ -40270,7 +40270,7 @@
       </c>
       <c r="BD208" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF208" t="inlineStr">
@@ -40471,7 +40471,7 @@
       </c>
       <c r="BD209" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF209" t="inlineStr">
@@ -40627,7 +40627,7 @@
       </c>
       <c r="BD210" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BH210" t="inlineStr">
@@ -40813,7 +40813,7 @@
       </c>
       <c r="BD211" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF211" t="inlineStr">
@@ -41004,7 +41004,7 @@
       </c>
       <c r="BD212" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF212" t="inlineStr">
@@ -41190,7 +41190,7 @@
       </c>
       <c r="BD213" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF213" t="inlineStr">
@@ -41381,7 +41381,7 @@
       </c>
       <c r="BD214" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF214" t="inlineStr">
@@ -41572,7 +41572,7 @@
       </c>
       <c r="BD215" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF215" t="inlineStr">
@@ -41773,7 +41773,7 @@
       </c>
       <c r="BD216" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF216" t="inlineStr">
@@ -41959,7 +41959,7 @@
       </c>
       <c r="BD217" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF217" t="inlineStr">
@@ -42150,7 +42150,7 @@
       </c>
       <c r="BD218" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF218" t="inlineStr">
@@ -42336,7 +42336,7 @@
       </c>
       <c r="BD219" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF219" t="inlineStr">
@@ -42527,7 +42527,7 @@
       </c>
       <c r="BD220" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF220" t="inlineStr">
@@ -42718,7 +42718,7 @@
       </c>
       <c r="BD221" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF221" t="inlineStr">
@@ -42909,7 +42909,7 @@
       </c>
       <c r="BD222" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF222" t="inlineStr">
@@ -43100,7 +43100,7 @@
       </c>
       <c r="BD223" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF223" t="inlineStr">
@@ -43291,7 +43291,7 @@
       </c>
       <c r="BD224" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF224" t="inlineStr">
@@ -43482,7 +43482,7 @@
       </c>
       <c r="BD225" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF225" t="inlineStr">
@@ -43673,7 +43673,7 @@
       </c>
       <c r="BD226" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF226" t="inlineStr">
@@ -43864,7 +43864,7 @@
       </c>
       <c r="BD227" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF227" t="inlineStr">
@@ -44055,7 +44055,7 @@
       </c>
       <c r="BD228" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF228" t="inlineStr">
@@ -44246,7 +44246,7 @@
       </c>
       <c r="BD229" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF229" t="inlineStr">
@@ -44437,7 +44437,7 @@
       </c>
       <c r="BD230" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF230" t="inlineStr">
@@ -44628,7 +44628,7 @@
       </c>
       <c r="BD231" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF231" t="inlineStr">
@@ -44819,7 +44819,7 @@
       </c>
       <c r="BD232" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF232" t="inlineStr">
@@ -45010,7 +45010,7 @@
       </c>
       <c r="BD233" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF233" t="inlineStr">
@@ -45201,7 +45201,7 @@
       </c>
       <c r="BD234" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF234" t="inlineStr">
@@ -45402,7 +45402,7 @@
       </c>
       <c r="BD235" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF235" t="inlineStr">
@@ -45593,7 +45593,7 @@
       </c>
       <c r="BD236" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF236" t="inlineStr">
@@ -45784,7 +45784,7 @@
       </c>
       <c r="BD237" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF237" t="inlineStr">
@@ -45975,7 +45975,7 @@
       </c>
       <c r="BD238" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF238" t="inlineStr">
@@ -46166,7 +46166,7 @@
       </c>
       <c r="BD239" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF239" t="inlineStr">
@@ -46357,7 +46357,7 @@
       </c>
       <c r="BD240" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF240" t="inlineStr">
@@ -46538,7 +46538,7 @@
       </c>
       <c r="BD241" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF241" t="inlineStr">
@@ -46724,7 +46724,7 @@
       </c>
       <c r="BD242" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF242" t="inlineStr">
@@ -46915,7 +46915,7 @@
       </c>
       <c r="BD243" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF243" t="inlineStr">
@@ -47101,7 +47101,7 @@
       </c>
       <c r="BD244" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF244" t="inlineStr">
@@ -47302,7 +47302,7 @@
       </c>
       <c r="BD245" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF245" t="inlineStr">
@@ -47494,7 +47494,7 @@
       </c>
       <c r="BD246" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF246" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="BD247" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF247" t="inlineStr">
@@ -47876,7 +47876,7 @@
       </c>
       <c r="BD248" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF248" t="inlineStr">
@@ -48067,7 +48067,7 @@
       </c>
       <c r="BD249" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF249" t="inlineStr">
@@ -48258,7 +48258,7 @@
       </c>
       <c r="BD250" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF250" t="inlineStr">
@@ -48449,7 +48449,7 @@
       </c>
       <c r="BD251" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF251" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="BD252" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF252" t="inlineStr">
@@ -48811,7 +48811,7 @@
       </c>
       <c r="BD253" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF253" t="inlineStr">
@@ -48992,7 +48992,7 @@
       </c>
       <c r="BD254" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF254" t="inlineStr">
@@ -49173,7 +49173,7 @@
       </c>
       <c r="BD255" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF255" t="inlineStr">
@@ -49364,7 +49364,7 @@
       </c>
       <c r="BD256" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF256" t="inlineStr">
@@ -49555,7 +49555,7 @@
       </c>
       <c r="BD257" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF257" t="inlineStr">
@@ -49746,7 +49746,7 @@
       </c>
       <c r="BD258" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF258" t="inlineStr">
@@ -49937,7 +49937,7 @@
       </c>
       <c r="BD259" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF259" t="inlineStr">
@@ -50098,7 +50098,7 @@
       </c>
       <c r="BD260" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BH260" t="inlineStr">
@@ -50284,7 +50284,7 @@
       </c>
       <c r="BD261" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF261" t="inlineStr">
@@ -50465,7 +50465,7 @@
       </c>
       <c r="BD262" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF262" t="inlineStr">
@@ -50656,7 +50656,7 @@
       </c>
       <c r="BD263" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF263" t="inlineStr">
@@ -50847,7 +50847,7 @@
       </c>
       <c r="BD264" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF264" t="inlineStr">
@@ -51038,7 +51038,7 @@
       </c>
       <c r="BD265" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF265" t="inlineStr">
@@ -51229,7 +51229,7 @@
       </c>
       <c r="BD266" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF266" t="inlineStr">
@@ -51420,7 +51420,7 @@
       </c>
       <c r="BD267" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF267" t="inlineStr">
@@ -51611,7 +51611,7 @@
       </c>
       <c r="BD268" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF268" t="inlineStr">
@@ -51802,7 +51802,7 @@
       </c>
       <c r="BD269" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF269" t="inlineStr">
@@ -51993,7 +51993,7 @@
       </c>
       <c r="BD270" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF270" t="inlineStr">
@@ -52184,7 +52184,7 @@
       </c>
       <c r="BD271" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF271" t="inlineStr">
@@ -52375,7 +52375,7 @@
       </c>
       <c r="BD272" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF272" t="inlineStr">
@@ -52566,7 +52566,7 @@
       </c>
       <c r="BD273" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF273" t="inlineStr">
@@ -52757,7 +52757,7 @@
       </c>
       <c r="BD274" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF274" t="inlineStr">
@@ -52948,7 +52948,7 @@
       </c>
       <c r="BD275" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF275" t="inlineStr">
@@ -53139,7 +53139,7 @@
       </c>
       <c r="BD276" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF276" t="inlineStr">
@@ -53330,7 +53330,7 @@
       </c>
       <c r="BD277" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF277" t="inlineStr">
@@ -53521,7 +53521,7 @@
       </c>
       <c r="BD278" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF278" t="inlineStr">
@@ -53712,7 +53712,7 @@
       </c>
       <c r="BD279" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF279" t="inlineStr">
@@ -53903,7 +53903,7 @@
       </c>
       <c r="BD280" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF280" t="inlineStr">
@@ -54094,7 +54094,7 @@
       </c>
       <c r="BD281" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF281" t="inlineStr">
@@ -54295,7 +54295,7 @@
       </c>
       <c r="BD282" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF282" t="inlineStr">
@@ -54486,7 +54486,7 @@
       </c>
       <c r="BD283" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF283" t="inlineStr">
@@ -54687,7 +54687,7 @@
       </c>
       <c r="BD284" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF284" t="inlineStr">
@@ -54888,7 +54888,7 @@
       </c>
       <c r="BD285" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF285" t="inlineStr">
@@ -55089,7 +55089,7 @@
       </c>
       <c r="BD286" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF286" t="inlineStr">
@@ -55290,7 +55290,7 @@
       </c>
       <c r="BD287" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF287" t="inlineStr">
@@ -55491,7 +55491,7 @@
       </c>
       <c r="BD288" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF288" t="inlineStr">
@@ -55682,7 +55682,7 @@
       </c>
       <c r="BD289" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF289" t="inlineStr">
@@ -55873,7 +55873,7 @@
       </c>
       <c r="BD290" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF290" t="inlineStr">
@@ -56064,7 +56064,7 @@
       </c>
       <c r="BD291" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF291" t="inlineStr">
@@ -56255,7 +56255,7 @@
       </c>
       <c r="BD292" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF292" t="inlineStr">
@@ -56446,7 +56446,7 @@
       </c>
       <c r="BD293" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF293" t="inlineStr">
@@ -56637,7 +56637,7 @@
       </c>
       <c r="BD294" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF294" t="inlineStr">
@@ -56828,7 +56828,7 @@
       </c>
       <c r="BD295" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF295" t="inlineStr">
@@ -57019,7 +57019,7 @@
       </c>
       <c r="BD296" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF296" t="inlineStr">
@@ -57210,7 +57210,7 @@
       </c>
       <c r="BD297" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF297" t="inlineStr">
@@ -57401,7 +57401,7 @@
       </c>
       <c r="BD298" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF298" t="inlineStr">
@@ -57592,7 +57592,7 @@
       </c>
       <c r="BD299" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF299" t="inlineStr">
@@ -57783,7 +57783,7 @@
       </c>
       <c r="BD300" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF300" t="inlineStr">
@@ -57974,7 +57974,7 @@
       </c>
       <c r="BD301" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF301" t="inlineStr">
@@ -58170,7 +58170,7 @@
       </c>
       <c r="BD302" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF302" t="inlineStr">
@@ -58366,7 +58366,7 @@
       </c>
       <c r="BD303" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF303" t="inlineStr">
@@ -58552,7 +58552,7 @@
       </c>
       <c r="BD304" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF304" t="inlineStr">
@@ -58738,7 +58738,7 @@
       </c>
       <c r="BD305" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF305" t="inlineStr">
@@ -58924,7 +58924,7 @@
       </c>
       <c r="BD306" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF306" t="inlineStr">
@@ -59110,7 +59110,7 @@
       </c>
       <c r="BD307" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF307" t="inlineStr">
@@ -59301,7 +59301,7 @@
       </c>
       <c r="BD308" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF308" t="inlineStr">
@@ -59472,7 +59472,7 @@
       </c>
       <c r="BD309" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF309" t="inlineStr">
@@ -59643,7 +59643,7 @@
       </c>
       <c r="BD310" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF310" t="inlineStr">
@@ -59814,7 +59814,7 @@
       </c>
       <c r="BD311" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF311" t="inlineStr">
@@ -59985,7 +59985,7 @@
       </c>
       <c r="BD312" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF312" t="inlineStr">
@@ -60156,7 +60156,7 @@
       </c>
       <c r="BD313" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF313" t="inlineStr">
@@ -60327,7 +60327,7 @@
       </c>
       <c r="BD314" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF314" t="inlineStr">
@@ -60503,7 +60503,7 @@
       </c>
       <c r="BD315" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF315" t="inlineStr">
@@ -60679,7 +60679,7 @@
       </c>
       <c r="BD316" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF316" t="inlineStr">
@@ -60855,7 +60855,7 @@
       </c>
       <c r="BD317" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF317" t="inlineStr">
@@ -61031,7 +61031,7 @@
       </c>
       <c r="BD318" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF318" t="inlineStr">
@@ -61207,7 +61207,7 @@
       </c>
       <c r="BD319" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF319" t="inlineStr">
@@ -61383,7 +61383,7 @@
       </c>
       <c r="BD320" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF320" t="inlineStr">
@@ -61559,7 +61559,7 @@
       </c>
       <c r="BD321" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF321" t="inlineStr">
@@ -61754,7 +61754,7 @@
       </c>
       <c r="BD322" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF322" t="inlineStr">
@@ -61939,7 +61939,7 @@
       </c>
       <c r="BD323" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF323" t="inlineStr">
@@ -62124,7 +62124,7 @@
       </c>
       <c r="BD324" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF324" t="inlineStr">
@@ -62309,7 +62309,7 @@
       </c>
       <c r="BD325" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF325" t="inlineStr">
@@ -62494,7 +62494,7 @@
       </c>
       <c r="BD326" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF326" t="inlineStr">
@@ -62679,7 +62679,7 @@
       </c>
       <c r="BD327" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF327" t="inlineStr">
@@ -62864,7 +62864,7 @@
       </c>
       <c r="BD328" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF328" t="inlineStr">
@@ -63049,7 +63049,7 @@
       </c>
       <c r="BD329" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF329" t="inlineStr">
@@ -63244,7 +63244,7 @@
       </c>
       <c r="BD330" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF330" t="inlineStr">
@@ -63434,7 +63434,7 @@
       </c>
       <c r="BD331" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF331" t="inlineStr">
@@ -63619,7 +63619,7 @@
       </c>
       <c r="BD332" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF332" t="inlineStr">
@@ -63809,7 +63809,7 @@
       </c>
       <c r="BD333" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF333" t="inlineStr">
@@ -64004,7 +64004,7 @@
       </c>
       <c r="BD334" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF334" t="inlineStr">
@@ -64189,7 +64189,7 @@
       </c>
       <c r="BD335" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF335" t="inlineStr">
@@ -64369,7 +64369,7 @@
       </c>
       <c r="BD336" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF336" t="inlineStr">
@@ -64554,7 +64554,7 @@
       </c>
       <c r="BD337" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF337" t="inlineStr">
@@ -64739,7 +64739,7 @@
       </c>
       <c r="BD338" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF338" t="inlineStr">
@@ -64924,7 +64924,7 @@
       </c>
       <c r="BD339" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF339" t="inlineStr">
@@ -65109,7 +65109,7 @@
       </c>
       <c r="BD340" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF340" t="inlineStr">
@@ -65294,7 +65294,7 @@
       </c>
       <c r="BD341" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF341" t="inlineStr">
@@ -65479,7 +65479,7 @@
       </c>
       <c r="BD342" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF342" t="inlineStr">
@@ -65659,7 +65659,7 @@
       </c>
       <c r="BD343" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF343" t="inlineStr">
@@ -65839,7 +65839,7 @@
       </c>
       <c r="BD344" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF344" t="inlineStr">
@@ -65999,7 +65999,7 @@
       </c>
       <c r="BD345" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF345" t="inlineStr">
@@ -66159,7 +66159,7 @@
       </c>
       <c r="BD346" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF346" t="inlineStr">
@@ -66319,7 +66319,7 @@
       </c>
       <c r="BD347" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF347" t="inlineStr">
@@ -66479,7 +66479,7 @@
       </c>
       <c r="BD348" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF348" t="inlineStr">
@@ -66674,7 +66674,7 @@
       </c>
       <c r="BD349" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF349" t="inlineStr">
@@ -66859,7 +66859,7 @@
       </c>
       <c r="BD350" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF350" t="inlineStr">
@@ -67039,7 +67039,7 @@
       </c>
       <c r="BD351" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF351" t="inlineStr">
@@ -67219,7 +67219,7 @@
       </c>
       <c r="BD352" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF352" t="inlineStr">
@@ -67404,7 +67404,7 @@
       </c>
       <c r="BD353" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF353" t="inlineStr">
@@ -67554,7 +67554,7 @@
       </c>
       <c r="BD354" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BH354" t="inlineStr">
@@ -67729,7 +67729,7 @@
       </c>
       <c r="BD355" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF355" t="inlineStr">
@@ -68239,7 +68239,7 @@
       </c>
       <c r="BD358" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF358" t="inlineStr">
@@ -69301,7 +69301,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>مياه الحنفية | مياه الحنفية | مياه الحنفية</t>
+          <t>مياه صالحة للشرب | مياه صالحة للشرب | مياه صالحة للشرب</t>
         </is>
       </c>
     </row>

--- a/clean/chemistry/chem_water_analysis_2025.xlsx
+++ b/clean/chemistry/chem_water_analysis_2025.xlsx
@@ -458,7 +458,7 @@
     <col width="60" customWidth="1" min="12" max="12"/>
     <col width="29" customWidth="1" min="13" max="13"/>
     <col width="44" customWidth="1" min="14" max="14"/>
-    <col width="29" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
     <col width="29" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
@@ -26010,7 +26010,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>( Private Sample) عينة خاصة</t>
+          <t>عينة خاصة</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -26201,7 +26201,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>( Private Sample) عينة خاصة</t>
+          <t>عينة خاصة</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -26392,7 +26392,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>( Private Sample) عينة خاصة</t>
+          <t>عينة خاصة</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -26583,7 +26583,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>( Private Sample) عينة خاصة</t>
+          <t>عينة خاصة</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -26774,7 +26774,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>( Private Sample) عينة خاصة</t>
+          <t>عينة خاصة</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -28903,11 +28903,6 @@
           <t>الإمام عبدالله بن سعود بن عبدالعزيز</t>
         </is>
       </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>لا يوجد</t>
@@ -45276,7 +45271,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>( Private Sample) عينة خاصة</t>
+          <t>عينة خاصة</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -47951,7 +47946,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>( Private Sample) عينة خاصة</t>
+          <t>عينة خاصة</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
@@ -48142,7 +48137,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>( Private Sample) عينة خاصة</t>
+          <t>عينة خاصة</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
@@ -48333,7 +48328,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>( Private Sample) عينة خاصة</t>
+          <t>عينة خاصة</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
@@ -58049,7 +58044,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>( Private Sample) عينة خاصة</t>
+          <t>عينة خاصة</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -58245,7 +58240,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>( Private Sample) عينة خاصة</t>
+          <t>عينة خاصة</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -58441,7 +58436,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>( Private Sample) عينة خاصة</t>
+          <t>عينة خاصة</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -58627,7 +58622,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>( Private Sample) عينة خاصة</t>
+          <t>عينة خاصة</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -58813,7 +58808,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>( Private Sample) عينة خاصة</t>
+          <t>عينة خاصة</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -58999,7 +58994,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>( Private Sample) عينة خاصة</t>
+          <t>عينة خاصة</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -68568,10 +68563,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
